--- a/static/excel_templates/干部任免审批表.xlsx
+++ b/static/excel_templates/干部任免审批表.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hsy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\迅雷下载\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D58688-9CD2-49E6-941C-EB7FC0AD639F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477E3A2F-61E2-4BE9-84AE-FBB112581431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="干部任免审批表" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">干部任免审批表!$A$1:$I$27</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -55,7 +58,8 @@
     <t>健康状况</t>
   </si>
   <si>
-    <t>专业技术职务</t>
+    <t>专业技
+术职务</t>
   </si>
   <si>
     <t>熟悉专业有何特长</t>
@@ -140,7 +144,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -175,13 +179,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -201,7 +198,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -209,22 +206,23 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="新宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -235,7 +233,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -369,19 +367,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -393,16 +378,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -412,7 +394,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -422,11 +404,29 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -436,10 +436,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -449,6 +449,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -456,6 +463,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -463,9 +473,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -478,39 +485,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -518,74 +497,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -605,7 +516,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CEEACA"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -887,400 +798,401 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="4.875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="9.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="5.25" style="9" customWidth="1"/>
-    <col min="7" max="7" width="6.875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="4.875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="5.25" style="8" customWidth="1"/>
+    <col min="7" max="7" width="6.875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="31"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="A1" s="39"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9" ht="28.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="26"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="35"/>
     </row>
     <row r="5" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="27"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="36"/>
     </row>
     <row r="6" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="27"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="36"/>
     </row>
     <row r="7" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="28"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="37"/>
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="15"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="18" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="35"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="18" t="s">
+      <c r="D9" s="23"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="35"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" ht="288.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
-    </row>
-    <row r="14" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
+    </row>
+    <row r="14" spans="1:9" ht="93.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="31"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="1:9" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="18" t="s">
+      <c r="G17" s="14"/>
+      <c r="H17" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="27"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="42"/>
-    </row>
-    <row r="19" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="27"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="42"/>
-    </row>
-    <row r="20" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="27"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="42"/>
-    </row>
-    <row r="21" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="27"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="42"/>
-    </row>
-    <row r="22" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="27"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="42"/>
-    </row>
-    <row r="23" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="27"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="42"/>
-    </row>
-    <row r="24" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="27"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="42"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="36"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="36"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="36"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="36"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="36"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="36"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="18"/>
+    </row>
+    <row r="24" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="36"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" spans="1:9" ht="91.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="16"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="21"/>
     </row>
     <row r="26" spans="1:9" ht="109.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="18" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="11"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="43" t="s">
+      <c r="B27" s="29"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="43"/>
-      <c r="F27" s="46" t="s">
+      <c r="E27" s="29"/>
+      <c r="F27" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="6"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="D27:E27"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="H23:I23"/>
-    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="H26:I26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="B15:I15"/>
+    <mergeCell ref="I4:I7"/>
     <mergeCell ref="A17:A24"/>
-    <mergeCell ref="H8:I8"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="B17:C17"/>
@@ -1291,13 +1203,14 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H19:I19"/>
@@ -1306,8 +1219,6 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="H20:I20"/>
@@ -1321,13 +1232,13 @@
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="I4:I7"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.67" right="0.71" top="0.61" bottom="0.88" header="0.43" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;R-&amp;P--</oddFooter>
   </headerFooter>
